--- a/Entrega 02/resultado_focalizacion.xlsx
+++ b/Entrega 02/resultado_focalizacion.xlsx
@@ -65,82 +65,94 @@
     <t>mora recurrente / conducta peor que sus pares</t>
   </si>
   <si>
+    <t>CLI_029</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Construcción</t>
+  </si>
+  <si>
+    <t>conducta peor que sus pares</t>
+  </si>
+  <si>
     <t>CLI_123</t>
   </si>
   <si>
     <t>mora actual alta / mora recurrente / conducta peor que sus pares</t>
   </si>
   <si>
+    <t>CLI_023</t>
+  </si>
+  <si>
     <t>CLI_073</t>
   </si>
   <si>
-    <t>Construcción</t>
-  </si>
-  <si>
     <t>mora actual alta / conducta peor que sus pares</t>
   </si>
   <si>
-    <t>CLI_023</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
     <t>CLI_097</t>
   </si>
   <si>
     <t>Industria</t>
   </si>
   <si>
-    <t>CLI_029</t>
+    <t>CLI_066</t>
+  </si>
+  <si>
+    <t>CLI_092</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>CLI_128</t>
+  </si>
+  <si>
+    <t>Agro</t>
+  </si>
+  <si>
+    <t>CLI_070</t>
+  </si>
+  <si>
+    <t>CLI_004</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Comercio</t>
+  </si>
+  <si>
+    <t>CLI_119</t>
+  </si>
+  <si>
+    <t>CLI_134</t>
+  </si>
+  <si>
+    <t>CLI_026</t>
+  </si>
+  <si>
+    <t>EEFF desactualizados</t>
+  </si>
+  <si>
+    <t>CLI_133</t>
+  </si>
+  <si>
+    <t>mora actual alta / conducta peor que sus pares / EEFF desactualizados</t>
+  </si>
+  <si>
+    <t>CLI_074</t>
+  </si>
+  <si>
+    <t>CLI_028</t>
   </si>
   <si>
     <t>sin alertas</t>
   </si>
   <si>
-    <t>CLI_066</t>
-  </si>
-  <si>
-    <t>CLI_092</t>
-  </si>
-  <si>
-    <t>Transporte</t>
-  </si>
-  <si>
-    <t>CLI_004</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>Comercio</t>
-  </si>
-  <si>
-    <t>CLI_128</t>
-  </si>
-  <si>
-    <t>Agro</t>
-  </si>
-  <si>
-    <t>CLI_070</t>
-  </si>
-  <si>
-    <t>CLI_119</t>
-  </si>
-  <si>
-    <t>conducta peor que sus pares</t>
-  </si>
-  <si>
-    <t>CLI_134</t>
-  </si>
-  <si>
-    <t>CLI_133</t>
-  </si>
-  <si>
-    <t>mora actual alta / conducta peor que sus pares / EEFF desactualizados</t>
-  </si>
-  <si>
-    <t>CLI_074</t>
+    <t>CLI_045</t>
   </si>
   <si>
     <t>CLI_076</t>
@@ -149,25 +161,28 @@
     <t>CLI_105</t>
   </si>
   <si>
-    <t>CLI_045</t>
-  </si>
-  <si>
     <t>CLI_096</t>
   </si>
   <si>
-    <t>EEFF desactualizados</t>
-  </si>
-  <si>
-    <t>CLI_026</t>
+    <t>CLI_035</t>
+  </si>
+  <si>
+    <t>CLI_012</t>
+  </si>
+  <si>
+    <t>CLI_131</t>
+  </si>
+  <si>
+    <t>CLI_041</t>
+  </si>
+  <si>
+    <t>CLI_085</t>
   </si>
   <si>
     <t>CLI_106</t>
   </si>
   <si>
-    <t>CLI_085</t>
-  </si>
-  <si>
-    <t>CLI_131</t>
+    <t>CLI_050</t>
   </si>
   <si>
     <t>CLI_125</t>
@@ -176,307 +191,292 @@
     <t>mora recurrente / EEFF desactualizados</t>
   </si>
   <si>
+    <t>CLI_037</t>
+  </si>
+  <si>
     <t>CLI_082</t>
   </si>
   <si>
+    <t>CLI_126</t>
+  </si>
+  <si>
+    <t>mora recurrente</t>
+  </si>
+  <si>
+    <t>CLI_109</t>
+  </si>
+  <si>
+    <t>CLI_048</t>
+  </si>
+  <si>
+    <t>CLI_122</t>
+  </si>
+  <si>
+    <t>CLI_113</t>
+  </si>
+  <si>
     <t>CLI_005</t>
   </si>
   <si>
-    <t>CLI_122</t>
+    <t>CLI_030</t>
+  </si>
+  <si>
+    <t>CLI_007</t>
+  </si>
+  <si>
+    <t>conducta peor que sus pares / EEFF desactualizados</t>
   </si>
   <si>
     <t>CLI_115</t>
   </si>
   <si>
-    <t>CLI_126</t>
-  </si>
-  <si>
-    <t>mora recurrente</t>
-  </si>
-  <si>
-    <t>CLI_109</t>
-  </si>
-  <si>
-    <t>CLI_041</t>
-  </si>
-  <si>
-    <t>CLI_113</t>
+    <t>CLI_077</t>
+  </si>
+  <si>
+    <t>CLI_058</t>
+  </si>
+  <si>
+    <t>CLI_086</t>
+  </si>
+  <si>
+    <t>CLI_095</t>
   </si>
   <si>
     <t>CLI_065</t>
   </si>
   <si>
-    <t>CLI_007</t>
-  </si>
-  <si>
-    <t>conducta peor que sus pares / EEFF desactualizados</t>
-  </si>
-  <si>
-    <t>CLI_028</t>
+    <t>CLI_034</t>
+  </si>
+  <si>
+    <t>CLI_078</t>
+  </si>
+  <si>
+    <t>CLI_046</t>
+  </si>
+  <si>
+    <t>CLI_021</t>
+  </si>
+  <si>
+    <t>CLI_089</t>
+  </si>
+  <si>
+    <t>CLI_056</t>
+  </si>
+  <si>
+    <t>CLI_040</t>
+  </si>
+  <si>
+    <t>CLI_019</t>
+  </si>
+  <si>
+    <t>CLI_010</t>
+  </si>
+  <si>
+    <t>CLI_033</t>
+  </si>
+  <si>
+    <t>CLI_001</t>
+  </si>
+  <si>
+    <t>CLI_002</t>
   </si>
   <si>
     <t>CLI_003</t>
   </si>
   <si>
-    <t>CLI_048</t>
-  </si>
-  <si>
-    <t>CLI_077</t>
-  </si>
-  <si>
-    <t>CLI_002</t>
-  </si>
-  <si>
-    <t>CLI_086</t>
-  </si>
-  <si>
     <t>CLI_006</t>
   </si>
   <si>
-    <t>CLI_050</t>
-  </si>
-  <si>
-    <t>CLI_010</t>
-  </si>
-  <si>
-    <t>CLI_058</t>
-  </si>
-  <si>
-    <t>CLI_035</t>
-  </si>
-  <si>
-    <t>CLI_095</t>
-  </si>
-  <si>
-    <t>CLI_078</t>
-  </si>
-  <si>
-    <t>CLI_037</t>
+    <t>CLI_008</t>
+  </si>
+  <si>
+    <t>CLI_009</t>
+  </si>
+  <si>
+    <t>CLI_011</t>
+  </si>
+  <si>
+    <t>CLI_013</t>
+  </si>
+  <si>
+    <t>CLI_014</t>
+  </si>
+  <si>
+    <t>CLI_015</t>
+  </si>
+  <si>
+    <t>CLI_016</t>
+  </si>
+  <si>
+    <t>CLI_017</t>
+  </si>
+  <si>
+    <t>CLI_018</t>
+  </si>
+  <si>
+    <t>CLI_020</t>
+  </si>
+  <si>
+    <t>CLI_022</t>
+  </si>
+  <si>
+    <t>CLI_024</t>
+  </si>
+  <si>
+    <t>CLI_025</t>
+  </si>
+  <si>
+    <t>CLI_027</t>
+  </si>
+  <si>
+    <t>CLI_031</t>
+  </si>
+  <si>
+    <t>CLI_032</t>
+  </si>
+  <si>
+    <t>CLI_036</t>
+  </si>
+  <si>
+    <t>CLI_038</t>
+  </si>
+  <si>
+    <t>CLI_039</t>
+  </si>
+  <si>
+    <t>CLI_042</t>
+  </si>
+  <si>
+    <t>CLI_043</t>
+  </si>
+  <si>
+    <t>CLI_044</t>
+  </si>
+  <si>
+    <t>CLI_047</t>
+  </si>
+  <si>
+    <t>CLI_049</t>
+  </si>
+  <si>
+    <t>CLI_051</t>
+  </si>
+  <si>
+    <t>CLI_052</t>
+  </si>
+  <si>
+    <t>CLI_053</t>
+  </si>
+  <si>
+    <t>CLI_054</t>
+  </si>
+  <si>
+    <t>CLI_055</t>
+  </si>
+  <si>
+    <t>CLI_057</t>
+  </si>
+  <si>
+    <t>CLI_059</t>
+  </si>
+  <si>
+    <t>CLI_060</t>
+  </si>
+  <si>
+    <t>CLI_061</t>
+  </si>
+  <si>
+    <t>CLI_062</t>
+  </si>
+  <si>
+    <t>CLI_063</t>
+  </si>
+  <si>
+    <t>CLI_064</t>
+  </si>
+  <si>
+    <t>CLI_067</t>
+  </si>
+  <si>
+    <t>CLI_068</t>
+  </si>
+  <si>
+    <t>CLI_069</t>
+  </si>
+  <si>
+    <t>CLI_071</t>
+  </si>
+  <si>
+    <t>CLI_072</t>
+  </si>
+  <si>
+    <t>CLI_075</t>
+  </si>
+  <si>
+    <t>CLI_079</t>
+  </si>
+  <si>
+    <t>CLI_080</t>
+  </si>
+  <si>
+    <t>CLI_083</t>
+  </si>
+  <si>
+    <t>CLI_084</t>
+  </si>
+  <si>
+    <t>CLI_087</t>
+  </si>
+  <si>
+    <t>CLI_088</t>
+  </si>
+  <si>
+    <t>CLI_090</t>
+  </si>
+  <si>
+    <t>CLI_091</t>
+  </si>
+  <si>
+    <t>CLI_093</t>
+  </si>
+  <si>
+    <t>CLI_094</t>
+  </si>
+  <si>
+    <t>CLI_098</t>
+  </si>
+  <si>
+    <t>CLI_099</t>
+  </si>
+  <si>
+    <t>CLI_100</t>
+  </si>
+  <si>
+    <t>CLI_101</t>
+  </si>
+  <si>
+    <t>CLI_102</t>
+  </si>
+  <si>
+    <t>CLI_103</t>
+  </si>
+  <si>
+    <t>CLI_104</t>
+  </si>
+  <si>
+    <t>CLI_107</t>
+  </si>
+  <si>
+    <t>CLI_108</t>
+  </si>
+  <si>
+    <t>CLI_110</t>
+  </si>
+  <si>
+    <t>CLI_111</t>
   </si>
   <si>
     <t>CLI_112</t>
-  </si>
-  <si>
-    <t>CLI_089</t>
-  </si>
-  <si>
-    <t>CLI_012</t>
-  </si>
-  <si>
-    <t>CLI_008</t>
-  </si>
-  <si>
-    <t>CLI_001</t>
-  </si>
-  <si>
-    <t>CLI_009</t>
-  </si>
-  <si>
-    <t>CLI_011</t>
-  </si>
-  <si>
-    <t>CLI_013</t>
-  </si>
-  <si>
-    <t>CLI_014</t>
-  </si>
-  <si>
-    <t>CLI_015</t>
-  </si>
-  <si>
-    <t>CLI_016</t>
-  </si>
-  <si>
-    <t>CLI_017</t>
-  </si>
-  <si>
-    <t>CLI_018</t>
-  </si>
-  <si>
-    <t>CLI_019</t>
-  </si>
-  <si>
-    <t>CLI_020</t>
-  </si>
-  <si>
-    <t>CLI_021</t>
-  </si>
-  <si>
-    <t>CLI_022</t>
-  </si>
-  <si>
-    <t>CLI_024</t>
-  </si>
-  <si>
-    <t>CLI_025</t>
-  </si>
-  <si>
-    <t>CLI_027</t>
-  </si>
-  <si>
-    <t>CLI_030</t>
-  </si>
-  <si>
-    <t>CLI_031</t>
-  </si>
-  <si>
-    <t>CLI_032</t>
-  </si>
-  <si>
-    <t>CLI_033</t>
-  </si>
-  <si>
-    <t>CLI_034</t>
-  </si>
-  <si>
-    <t>CLI_036</t>
-  </si>
-  <si>
-    <t>CLI_038</t>
-  </si>
-  <si>
-    <t>CLI_039</t>
-  </si>
-  <si>
-    <t>CLI_040</t>
-  </si>
-  <si>
-    <t>CLI_042</t>
-  </si>
-  <si>
-    <t>CLI_043</t>
-  </si>
-  <si>
-    <t>CLI_044</t>
-  </si>
-  <si>
-    <t>CLI_046</t>
-  </si>
-  <si>
-    <t>CLI_047</t>
-  </si>
-  <si>
-    <t>CLI_049</t>
-  </si>
-  <si>
-    <t>CLI_051</t>
-  </si>
-  <si>
-    <t>CLI_052</t>
-  </si>
-  <si>
-    <t>CLI_053</t>
-  </si>
-  <si>
-    <t>CLI_054</t>
-  </si>
-  <si>
-    <t>CLI_055</t>
-  </si>
-  <si>
-    <t>CLI_056</t>
-  </si>
-  <si>
-    <t>CLI_057</t>
-  </si>
-  <si>
-    <t>CLI_059</t>
-  </si>
-  <si>
-    <t>CLI_060</t>
-  </si>
-  <si>
-    <t>CLI_061</t>
-  </si>
-  <si>
-    <t>CLI_062</t>
-  </si>
-  <si>
-    <t>CLI_063</t>
-  </si>
-  <si>
-    <t>CLI_064</t>
-  </si>
-  <si>
-    <t>CLI_067</t>
-  </si>
-  <si>
-    <t>CLI_068</t>
-  </si>
-  <si>
-    <t>CLI_069</t>
-  </si>
-  <si>
-    <t>CLI_071</t>
-  </si>
-  <si>
-    <t>CLI_072</t>
-  </si>
-  <si>
-    <t>CLI_075</t>
-  </si>
-  <si>
-    <t>CLI_079</t>
-  </si>
-  <si>
-    <t>CLI_080</t>
-  </si>
-  <si>
-    <t>CLI_083</t>
-  </si>
-  <si>
-    <t>CLI_084</t>
-  </si>
-  <si>
-    <t>CLI_087</t>
-  </si>
-  <si>
-    <t>CLI_088</t>
-  </si>
-  <si>
-    <t>CLI_090</t>
-  </si>
-  <si>
-    <t>CLI_091</t>
-  </si>
-  <si>
-    <t>CLI_093</t>
-  </si>
-  <si>
-    <t>CLI_094</t>
-  </si>
-  <si>
-    <t>CLI_098</t>
-  </si>
-  <si>
-    <t>CLI_099</t>
-  </si>
-  <si>
-    <t>CLI_100</t>
-  </si>
-  <si>
-    <t>CLI_101</t>
-  </si>
-  <si>
-    <t>CLI_102</t>
-  </si>
-  <si>
-    <t>CLI_103</t>
-  </si>
-  <si>
-    <t>CLI_104</t>
-  </si>
-  <si>
-    <t>CLI_107</t>
-  </si>
-  <si>
-    <t>CLI_108</t>
-  </si>
-  <si>
-    <t>CLI_110</t>
-  </si>
-  <si>
-    <t>CLI_111</t>
   </si>
   <si>
     <t>CLI_114</t>
@@ -925,7 +925,7 @@
         <v>11.86363636363636</v>
       </c>
       <c r="H2">
-        <v>2.034876741210771</v>
+        <v>1.930033868128712</v>
       </c>
       <c r="I2">
         <v>422.46</v>
@@ -934,7 +934,7 @@
         <v>228.8325</v>
       </c>
       <c r="K2">
-        <v>83.67822386794991</v>
+        <v>80.19208626380158</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
@@ -945,83 +945,83 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>1810</v>
+        <v>6870</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>6.863636363636363</v>
       </c>
       <c r="H3">
-        <v>4.292818760516196</v>
+        <v>1.19276424565445</v>
       </c>
       <c r="I3">
-        <v>162.9</v>
+        <v>293.6925</v>
       </c>
       <c r="J3">
-        <v>88.23750000000001</v>
+        <v>324.6075</v>
       </c>
       <c r="K3">
-        <v>68.0694730361225</v>
+        <v>70.30108679984941</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>2676</v>
+        <v>1810</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G4">
-        <v>7.409090909090909</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>2.655439068818783</v>
+        <v>4.187975887434137</v>
       </c>
       <c r="I4">
-        <v>240.84</v>
+        <v>162.9</v>
       </c>
       <c r="J4">
-        <v>130.455</v>
+        <v>88.23750000000001</v>
       </c>
       <c r="K4">
-        <v>62.25205752140643</v>
+        <v>67.09748536045305</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -1039,7 +1039,7 @@
         <v>17.72727272727273</v>
       </c>
       <c r="H5">
-        <v>5.142786240487477</v>
+        <v>5.507457103381594</v>
       </c>
       <c r="I5">
         <v>54.9765</v>
@@ -1048,7 +1048,7 @@
         <v>60.76349999999999</v>
       </c>
       <c r="K5">
-        <v>56.15622365182658</v>
+        <v>60.76349999999999</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1062,34 +1062,34 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>2676</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>46</v>
+      </c>
+      <c r="G6">
+        <v>7.409090909090909</v>
+      </c>
+      <c r="H6">
+        <v>2.550596195736724</v>
+      </c>
+      <c r="I6">
+        <v>240.84</v>
+      </c>
+      <c r="J6">
+        <v>130.455</v>
+      </c>
+      <c r="K6">
+        <v>60.41590891566496</v>
+      </c>
+      <c r="L6" t="s">
         <v>24</v>
-      </c>
-      <c r="D6">
-        <v>1061</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>99</v>
-      </c>
-      <c r="G6">
-        <v>6.909090909090909</v>
-      </c>
-      <c r="H6">
-        <v>5.210281994126727</v>
-      </c>
-      <c r="I6">
-        <v>95.48999999999999</v>
-      </c>
-      <c r="J6">
-        <v>51.72375000000001</v>
-      </c>
-      <c r="K6">
-        <v>48.42926449016526</v>
-      </c>
-      <c r="L6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1097,37 +1097,37 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>6870</v>
+        <v>1061</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G7">
-        <v>6.863636363636363</v>
+        <v>6.909090909090909</v>
       </c>
       <c r="H7">
-        <v>0.828093382760332</v>
+        <v>5.105439121044667</v>
       </c>
       <c r="I7">
-        <v>293.6925</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="J7">
-        <v>324.6075</v>
+        <v>51.72375000000001</v>
       </c>
       <c r="K7">
-        <v>48.30526894659204</v>
+        <v>47.9481640583261</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1153,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>3.654336365121161</v>
+        <v>3.549493492039102</v>
       </c>
       <c r="I8">
         <v>133.29</v>
@@ -1162,10 +1162,10 @@
         <v>72.19875000000002</v>
       </c>
       <c r="K8">
-        <v>47.41271647084405</v>
+        <v>46.53127358922293</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1191,7 +1191,7 @@
         <v>15.22727272727273</v>
       </c>
       <c r="H9">
-        <v>3.370806747368967</v>
+        <v>3.265963874286908</v>
       </c>
       <c r="I9">
         <v>84.78</v>
@@ -1200,7 +1200,7 @@
         <v>45.92250000000001</v>
       </c>
       <c r="K9">
-        <v>27.81736683556992</v>
+        <v>27.23239113834435</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -1211,113 +1211,113 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10">
-        <v>1696</v>
+        <v>607</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G10">
-        <v>4.636363636363637</v>
+        <v>7.227272727272728</v>
       </c>
       <c r="H10">
-        <v>3.112316554338893</v>
+        <v>3.881073048181578</v>
       </c>
       <c r="I10">
-        <v>29.68</v>
+        <v>54.63</v>
       </c>
       <c r="J10">
-        <v>42.824</v>
+        <v>29.59125000000002</v>
       </c>
       <c r="K10">
-        <v>23.95121964226221</v>
+        <v>20.8527820882141</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>607</v>
+        <v>1412</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G11">
-        <v>7.227272727272728</v>
+        <v>4.909090909090909</v>
       </c>
       <c r="H11">
-        <v>3.985915921263637</v>
+        <v>1.505723790205956</v>
       </c>
       <c r="I11">
-        <v>54.63</v>
+        <v>127.08</v>
       </c>
       <c r="J11">
-        <v>29.59125000000002</v>
+        <v>68.83500000000002</v>
       </c>
       <c r="K11">
-        <v>21.19571566282702</v>
+        <v>18.81930174911173</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
       <c r="D12">
-        <v>1412</v>
+        <v>1696</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12">
-        <v>4.909090909090909</v>
+        <v>4.636363636363637</v>
       </c>
       <c r="H12">
-        <v>1.610566663288016</v>
+        <v>2.349822931923914</v>
       </c>
       <c r="I12">
-        <v>127.08</v>
+        <v>29.68</v>
       </c>
       <c r="J12">
-        <v>68.83500000000002</v>
+        <v>42.824</v>
       </c>
       <c r="K12">
-        <v>19.92253793989338</v>
+        <v>18.27137558183128</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>1589</v>
@@ -1343,7 +1343,7 @@
         <v>7.227272727272728</v>
       </c>
       <c r="H13">
-        <v>1.232488805851096</v>
+        <v>1.127645932769036</v>
       </c>
       <c r="I13">
         <v>143.01</v>
@@ -1352,21 +1352,21 @@
         <v>77.46375000000003</v>
       </c>
       <c r="K13">
-        <v>17.15687317794158</v>
+        <v>15.86061969886307</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>865</v>
@@ -1381,7 +1381,7 @@
         <v>5.636363636363637</v>
       </c>
       <c r="H14">
-        <v>2.055270759372599</v>
+        <v>1.95042788629054</v>
       </c>
       <c r="I14">
         <v>77.84999999999999</v>
@@ -1390,86 +1390,86 @@
         <v>42.16875000000002</v>
       </c>
       <c r="K14">
-        <v>15.57458241921985</v>
+        <v>14.93377150037433</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>1491</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
+        <v>3.818181818181818</v>
+      </c>
+      <c r="H15">
+        <v>0.9183321869756514</v>
+      </c>
+      <c r="I15">
+        <v>63.74025</v>
+      </c>
+      <c r="J15">
+        <v>70.44974999999999</v>
+      </c>
+      <c r="K15">
+        <v>11.74703166542399</v>
+      </c>
+      <c r="L15" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
-        <v>226</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>102</v>
-      </c>
-      <c r="G15">
-        <v>7.409090909090909</v>
-      </c>
-      <c r="H15">
-        <v>5.564720549254675</v>
-      </c>
-      <c r="I15">
-        <v>20.34</v>
-      </c>
-      <c r="J15">
-        <v>11.0175</v>
-      </c>
-      <c r="K15">
-        <v>11.0175</v>
-      </c>
-      <c r="L15" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>226</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>102</v>
+      </c>
+      <c r="G16">
+        <v>7.409090909090909</v>
+      </c>
+      <c r="H16">
+        <v>5.459877676172615</v>
+      </c>
+      <c r="I16">
+        <v>20.34</v>
+      </c>
+      <c r="J16">
+        <v>11.0175</v>
+      </c>
+      <c r="K16">
+        <v>10.92231880667703</v>
+      </c>
+      <c r="L16" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16">
-        <v>678</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>20</v>
-      </c>
-      <c r="G16">
-        <v>8.681818181818182</v>
-      </c>
-      <c r="H16">
-        <v>1.810188267973559</v>
-      </c>
-      <c r="I16">
-        <v>61.02</v>
-      </c>
-      <c r="J16">
-        <v>33.05250000000001</v>
-      </c>
-      <c r="K16">
-        <v>10.75188721475146</v>
-      </c>
-      <c r="L16" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1480,34 +1480,34 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>455</v>
+        <v>678</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G17">
-        <v>6.818181818181818</v>
+        <v>8.681818181818182</v>
       </c>
       <c r="H17">
-        <v>2.420748662331532</v>
+        <v>1.705345394891499</v>
       </c>
       <c r="I17">
-        <v>40.95</v>
+        <v>61.02</v>
       </c>
       <c r="J17">
-        <v>22.18125000000001</v>
+        <v>33.05250000000001</v>
       </c>
       <c r="K17">
-        <v>9.649223315182132</v>
+        <v>10.23447438747048</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1515,45 +1515,45 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>1032</v>
+        <v>2489</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>6.863636363636363</v>
+        <v>5.045454545454546</v>
       </c>
       <c r="H18">
-        <v>1.036112485312696</v>
+        <v>0.4706399180013713</v>
       </c>
       <c r="I18">
-        <v>92.88</v>
+        <v>106.40475</v>
       </c>
       <c r="J18">
-        <v>50.31000000000003</v>
+        <v>117.60525</v>
       </c>
       <c r="K18">
-        <v>9.367374098069222</v>
+        <v>10.04996029520518</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -1571,7 +1571,7 @@
         <v>5.909090909090909</v>
       </c>
       <c r="H19">
-        <v>1.228249935859223</v>
+        <v>1.592920798753341</v>
       </c>
       <c r="I19">
         <v>30.22425</v>
@@ -1580,48 +1580,48 @@
         <v>33.40575</v>
       </c>
       <c r="K19">
-        <v>7.373346052449079</v>
+        <v>9.661938890142538</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D20">
-        <v>910</v>
+        <v>455</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G20">
-        <v>6.772727272727273</v>
+        <v>6.818181818181818</v>
       </c>
       <c r="H20">
-        <v>0.8961033589144752</v>
+        <v>2.315905789249474</v>
       </c>
       <c r="I20">
-        <v>81.89999999999999</v>
+        <v>40.95</v>
       </c>
       <c r="J20">
-        <v>44.36250000000003</v>
+        <v>22.18125000000001</v>
       </c>
       <c r="K20">
-        <v>7.14382418811092</v>
+        <v>9.327296486113125</v>
       </c>
       <c r="L20" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1629,37 +1629,37 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D21">
-        <v>1491</v>
+        <v>1032</v>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21">
-        <v>3.818181818181818</v>
+        <v>6.863636363636363</v>
       </c>
       <c r="H21">
-        <v>0.5536613240815337</v>
+        <v>0.9312696122306369</v>
       </c>
       <c r="I21">
-        <v>63.74025</v>
+        <v>92.88</v>
       </c>
       <c r="J21">
-        <v>70.44974999999999</v>
+        <v>50.31000000000003</v>
       </c>
       <c r="K21">
-        <v>7.009390951615226</v>
+        <v>8.507042962269466</v>
       </c>
       <c r="L21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1670,34 +1670,34 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D22">
-        <v>2473</v>
+        <v>910</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G22">
-        <v>4.863636363636364</v>
+        <v>6.772727272727273</v>
       </c>
       <c r="H22">
-        <v>0.2937271799020938</v>
+        <v>0.791260485832416</v>
       </c>
       <c r="I22">
-        <v>222.57</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="J22">
-        <v>120.55875</v>
+        <v>44.36250000000003</v>
       </c>
       <c r="K22">
-        <v>6.363550754541389</v>
+        <v>6.373593592074946</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1705,37 +1705,37 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D23">
-        <v>516</v>
+        <v>1581</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>3.454545454545455</v>
+        <v>4.954545454545454</v>
       </c>
       <c r="H23">
-        <v>1.188721566188904</v>
+        <v>0.434533701618717</v>
       </c>
       <c r="I23">
-        <v>46.44</v>
+        <v>67.58775</v>
       </c>
       <c r="J23">
-        <v>25.15500000000002</v>
+        <v>74.70224999999999</v>
       </c>
       <c r="K23">
-        <v>5.373547644092738</v>
+        <v>5.893944265460709</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1743,37 +1743,37 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D24">
-        <v>265</v>
+        <v>1567</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>6.590909090909091</v>
+        <v>4.818181818181818</v>
       </c>
       <c r="H24">
-        <v>2.278531666367114</v>
+        <v>0.3803743770447364</v>
       </c>
       <c r="I24">
-        <v>23.85</v>
+        <v>66.98925</v>
       </c>
       <c r="J24">
-        <v>12.91875000000001</v>
+        <v>74.04075</v>
       </c>
       <c r="K24">
-        <v>5.28971413826391</v>
+        <v>5.113649299217015</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1784,162 +1784,162 @@
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25">
-        <v>860</v>
+        <v>265</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G25">
-        <v>8.272727272727273</v>
+        <v>6.590909090909091</v>
       </c>
       <c r="H25">
-        <v>0.6086811940959406</v>
+        <v>2.173688793285055</v>
       </c>
       <c r="I25">
-        <v>77.39999999999999</v>
+        <v>23.85</v>
       </c>
       <c r="J25">
-        <v>41.92500000000003</v>
+        <v>12.91875000000001</v>
       </c>
       <c r="K25">
-        <v>4.585847364049624</v>
+        <v>5.098785441471581</v>
       </c>
       <c r="L25" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>370</v>
+        <v>690</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>7.181818181818182</v>
+        <v>3.227272727272728</v>
       </c>
       <c r="H26">
-        <v>1.110532787644201</v>
+        <v>0.8394961455117522</v>
       </c>
       <c r="I26">
-        <v>33.3</v>
+        <v>29.4975</v>
       </c>
       <c r="J26">
-        <v>18.03750000000001</v>
+        <v>32.60249999999999</v>
       </c>
       <c r="K26">
-        <v>3.599683933780866</v>
+        <v>4.969566275376314</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>516</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>48</v>
+      </c>
+      <c r="G27">
+        <v>3.454545454545455</v>
+      </c>
+      <c r="H27">
+        <v>1.083878693106845</v>
+      </c>
+      <c r="I27">
+        <v>46.44</v>
+      </c>
+      <c r="J27">
+        <v>25.15500000000002</v>
+      </c>
+      <c r="K27">
+        <v>4.95055485922204</v>
+      </c>
+      <c r="L27" t="s">
         <v>24</v>
-      </c>
-      <c r="D27">
-        <v>463</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>6.909090909090909</v>
-      </c>
-      <c r="H27">
-        <v>1.625205033547187</v>
-      </c>
-      <c r="I27">
-        <v>8.102500000000001</v>
-      </c>
-      <c r="J27">
-        <v>11.69075</v>
-      </c>
-      <c r="K27">
-        <v>3.414343196171202</v>
-      </c>
-      <c r="L27" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>1091</v>
+        <v>2473</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>7.590909090909092</v>
+        <v>4.863636363636364</v>
       </c>
       <c r="H28">
-        <v>0.3378845712260359</v>
+        <v>0.1888843068200346</v>
       </c>
       <c r="I28">
-        <v>98.19</v>
+        <v>222.57</v>
       </c>
       <c r="J28">
-        <v>53.18625000000003</v>
+        <v>120.55875</v>
       </c>
       <c r="K28">
-        <v>3.22941882118011</v>
+        <v>4.134695104725916</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D29">
-        <v>2101</v>
+        <v>863</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -1948,174 +1948,174 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>7.181818181818182</v>
+        <v>5.227272727272728</v>
       </c>
       <c r="H29">
-        <v>0.1754065975040928</v>
+        <v>0.5428523507666791</v>
       </c>
       <c r="I29">
-        <v>189.09</v>
+        <v>36.89325</v>
       </c>
       <c r="J29">
-        <v>102.42375</v>
+        <v>40.77675</v>
       </c>
       <c r="K29">
-        <v>3.22851818561062</v>
+        <v>4.019233228441084</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <v>860</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>8.272727272727273</v>
+      </c>
+      <c r="H30">
+        <v>0.5038383210138814</v>
+      </c>
+      <c r="I30">
+        <v>77.39999999999999</v>
+      </c>
+      <c r="J30">
+        <v>41.92500000000003</v>
+      </c>
+      <c r="K30">
+        <v>3.835421903792432</v>
+      </c>
+      <c r="L30" t="s">
         <v>57</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30">
-        <v>640</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>8.181818181818182</v>
-      </c>
-      <c r="H30">
-        <v>0.5725749777132864</v>
-      </c>
-      <c r="I30">
-        <v>57.59999999999999</v>
-      </c>
-      <c r="J30">
-        <v>31.20000000000002</v>
-      </c>
-      <c r="K30">
-        <v>3.210285071196836</v>
-      </c>
-      <c r="L30" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D31">
-        <v>559</v>
+        <v>918</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G31">
-        <v>5.636363636363637</v>
+        <v>2.772727272727273</v>
       </c>
       <c r="H31">
-        <v>0.6006300191546522</v>
+        <v>0.4511592435673474</v>
       </c>
       <c r="I31">
-        <v>50.31</v>
+        <v>39.2445</v>
       </c>
       <c r="J31">
-        <v>27.25125000000001</v>
+        <v>43.37549999999999</v>
       </c>
       <c r="K31">
-        <v>2.941373005995871</v>
+        <v>3.553229267521646</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D32">
-        <v>690</v>
+        <v>370</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G32">
-        <v>3.227272727272728</v>
+        <v>7.181818181818182</v>
       </c>
       <c r="H32">
-        <v>0.4748252826176345</v>
+        <v>1.005689914562142</v>
       </c>
       <c r="I32">
-        <v>29.4975</v>
+        <v>33.3</v>
       </c>
       <c r="J32">
-        <v>32.60249999999999</v>
+        <v>18.03750000000001</v>
       </c>
       <c r="K32">
-        <v>2.781899133931324</v>
+        <v>3.293740013476737</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33">
+        <v>640</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>8.181818181818182</v>
+      </c>
+      <c r="H33">
+        <v>0.4677321046312272</v>
+      </c>
+      <c r="I33">
+        <v>57.59999999999999</v>
+      </c>
+      <c r="J33">
+        <v>31.20000000000002</v>
+      </c>
+      <c r="K33">
+        <v>2.649724072391595</v>
+      </c>
+      <c r="L33" t="s">
         <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33">
-        <v>555</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>8.090909090909092</v>
-      </c>
-      <c r="H33">
-        <v>0.5364687613306326</v>
-      </c>
-      <c r="I33">
-        <v>49.95</v>
-      </c>
-      <c r="J33">
-        <v>27.05625000000001</v>
-      </c>
-      <c r="K33">
-        <v>2.608366906348247</v>
-      </c>
-      <c r="L33" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2126,34 +2126,34 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D34">
-        <v>1720</v>
+        <v>559</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>7.136363636363637</v>
+        <v>5.636363636363637</v>
       </c>
       <c r="H34">
-        <v>0.1573534893127662</v>
+        <v>0.495787146072593</v>
       </c>
       <c r="I34">
-        <v>154.8</v>
+        <v>50.31</v>
       </c>
       <c r="J34">
-        <v>83.85000000000005</v>
+        <v>27.25125000000001</v>
       </c>
       <c r="K34">
-        <v>2.371024737377448</v>
+        <v>2.453186508908997</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2161,51 +2161,51 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D35">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>6.363636363636363</v>
+        <v>6.590909090909091</v>
       </c>
       <c r="H35">
-        <v>2.239791015375804</v>
+        <v>1.084445596506488</v>
       </c>
       <c r="I35">
-        <v>3.885</v>
+        <v>10.73025</v>
       </c>
       <c r="J35">
-        <v>5.605500000000001</v>
+        <v>11.85975</v>
       </c>
       <c r="K35">
-        <v>2.256204678305126</v>
+        <v>2.335243547384322</v>
       </c>
       <c r="L35" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D36">
-        <v>2489</v>
+        <v>1091</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -2214,36 +2214,36 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>5.045454545454546</v>
+        <v>7.590909090909092</v>
       </c>
       <c r="H36">
-        <v>0.1059690551072535</v>
+        <v>0.2330416981439767</v>
       </c>
       <c r="I36">
-        <v>106.40475</v>
+        <v>98.19</v>
       </c>
       <c r="J36">
-        <v>117.60525</v>
+        <v>53.18625000000003</v>
       </c>
       <c r="K36">
-        <v>2.239558502146441</v>
+        <v>2.250514853815159</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37">
-        <v>881</v>
+        <v>555</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -2252,36 +2252,36 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>4.045454545454546</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="H37">
-        <v>0.487859217493588</v>
+        <v>0.4316258882485734</v>
       </c>
       <c r="I37">
-        <v>15.4175</v>
+        <v>49.95</v>
       </c>
       <c r="J37">
-        <v>22.24525</v>
+        <v>27.05625000000001</v>
       </c>
       <c r="K37">
-        <v>1.950241734852759</v>
+        <v>2.12043012223464</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D38">
-        <v>251</v>
+        <v>463</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -2290,98 +2290,98 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>6.590909090909091</v>
+        <v>6.909090909090909</v>
       </c>
       <c r="H38">
-        <v>0.7197747336123702</v>
+        <v>0.8627114111322068</v>
       </c>
       <c r="I38">
-        <v>10.73025</v>
+        <v>8.102500000000001</v>
       </c>
       <c r="J38">
-        <v>11.85975</v>
+        <v>11.69075</v>
       </c>
       <c r="K38">
-        <v>1.534012053507816</v>
+        <v>1.831288603864235</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>405</v>
+        <v>718</v>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>5.454545454545455</v>
+        <v>4.590909090909091</v>
       </c>
       <c r="H39">
-        <v>0.4245146763737769</v>
+        <v>0.2901088360881014</v>
       </c>
       <c r="I39">
-        <v>36.45</v>
+        <v>30.6945</v>
       </c>
       <c r="J39">
-        <v>19.74375000000001</v>
+        <v>33.9255</v>
       </c>
       <c r="K39">
-        <v>1.506187339951394</v>
+        <v>1.787047476532103</v>
       </c>
       <c r="L39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40">
+        <v>222</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>16</v>
+      </c>
+      <c r="G40">
+        <v>6.363636363636363</v>
+      </c>
+      <c r="H40">
+        <v>1.477297392960824</v>
+      </c>
+      <c r="I40">
+        <v>3.885</v>
+      </c>
+      <c r="J40">
+        <v>5.605500000000001</v>
+      </c>
+      <c r="K40">
+        <v>1.503596011879484</v>
+      </c>
+      <c r="L40" t="s">
         <v>69</v>
-      </c>
-      <c r="B40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40">
-        <v>453</v>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>17</v>
-      </c>
-      <c r="G40">
-        <v>2.409090909090909</v>
-      </c>
-      <c r="H40">
-        <v>0.7211220577381231</v>
-      </c>
-      <c r="I40">
-        <v>7.927500000000001</v>
-      </c>
-      <c r="J40">
-        <v>11.43825</v>
-      </c>
-      <c r="K40">
-        <v>1.482262101738038</v>
-      </c>
-      <c r="L40" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2392,34 +2392,34 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D41">
-        <v>370</v>
+        <v>2101</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>5.636363636363637</v>
+        <v>7.181818181818182</v>
       </c>
       <c r="H41">
-        <v>0.4447756541313009</v>
+        <v>0.07056372442203365</v>
       </c>
       <c r="I41">
-        <v>33.3</v>
+        <v>189.09</v>
       </c>
       <c r="J41">
-        <v>18.03750000000001</v>
+        <v>102.42375</v>
       </c>
       <c r="K41">
-        <v>1.441696989162893</v>
+        <v>1.312293701721912</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2427,37 +2427,37 @@
         <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D42">
-        <v>676</v>
+        <v>405</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G42">
-        <v>3.909090909090909</v>
+        <v>5.454545454545455</v>
       </c>
       <c r="H42">
-        <v>0.4336998929196069</v>
+        <v>0.3196718032917177</v>
       </c>
       <c r="I42">
-        <v>11.83</v>
+        <v>36.45</v>
       </c>
       <c r="J42">
-        <v>17.069</v>
+        <v>19.74375000000001</v>
       </c>
       <c r="K42">
-        <v>1.330313608153474</v>
+        <v>1.145995338277907</v>
       </c>
       <c r="L42" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2465,37 +2465,37 @@
         <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>863</v>
+        <v>66</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G43">
-        <v>5.227272727272728</v>
+        <v>6.181818181818182</v>
       </c>
       <c r="H43">
-        <v>0.1781814878725613</v>
+        <v>1.907307909547544</v>
       </c>
       <c r="I43">
-        <v>36.89325</v>
+        <v>5.94</v>
       </c>
       <c r="J43">
-        <v>40.77675</v>
+        <v>3.217500000000001</v>
       </c>
       <c r="K43">
-        <v>1.305665203004778</v>
+        <v>1.114264366253754</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2503,37 +2503,37 @@
         <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D44">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G44">
-        <v>4.954545454545454</v>
+        <v>5.636363636363637</v>
       </c>
       <c r="H44">
-        <v>0.8489213813201271</v>
+        <v>0.3399327810492417</v>
       </c>
       <c r="I44">
-        <v>5.635000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="J44">
-        <v>8.130500000000001</v>
+        <v>18.03750000000001</v>
       </c>
       <c r="K44">
-        <v>1.240341761950248</v>
+        <v>1.113315532573266</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2544,34 +2544,34 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D45">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G45">
-        <v>6.181818181818182</v>
+        <v>6.545454545454546</v>
       </c>
       <c r="H45">
-        <v>2.012150782629603</v>
+        <v>0.700994944875781</v>
       </c>
       <c r="I45">
-        <v>5.94</v>
+        <v>11.79</v>
       </c>
       <c r="J45">
-        <v>3.217500000000001</v>
+        <v>6.386250000000004</v>
       </c>
       <c r="K45">
-        <v>1.163417836674274</v>
+        <v>0.8128486309887434</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2579,13 +2579,13 @@
         <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D46">
-        <v>1581</v>
+        <v>1720</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -2594,22 +2594,22 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>4.954545454545454</v>
+        <v>7.136363636363637</v>
       </c>
       <c r="H46">
-        <v>0.0698628387245992</v>
+        <v>0.05251061623070699</v>
       </c>
       <c r="I46">
-        <v>67.58775</v>
+        <v>154.8</v>
       </c>
       <c r="J46">
-        <v>74.70224999999999</v>
+        <v>83.85000000000005</v>
       </c>
       <c r="K46">
-        <v>0.9378568425711329</v>
+        <v>0.7994642696792535</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2617,37 +2617,37 @@
         <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D47">
-        <v>131</v>
+        <v>314</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>6.545454545454546</v>
+        <v>4.454545454545455</v>
       </c>
       <c r="H47">
-        <v>0.8058378179578402</v>
+        <v>0.2359495115141207</v>
       </c>
       <c r="I47">
-        <v>11.79</v>
+        <v>13.4235</v>
       </c>
       <c r="J47">
-        <v>6.386250000000004</v>
+        <v>14.8365</v>
       </c>
       <c r="K47">
-        <v>0.9248050678164855</v>
+        <v>0.6356227314834343</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2658,7 +2658,7 @@
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D48">
         <v>129</v>
@@ -2673,7 +2673,7 @@
         <v>8.272727272727273</v>
       </c>
       <c r="H48">
-        <v>0.6086811940959406</v>
+        <v>0.5038383210138814</v>
       </c>
       <c r="I48">
         <v>11.61</v>
@@ -2682,10 +2682,10 @@
         <v>6.288750000000004</v>
       </c>
       <c r="K48">
-        <v>0.6878771046074434</v>
+        <v>0.5753132855688649</v>
       </c>
       <c r="L48" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2693,37 +2693,37 @@
         <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D49">
-        <v>918</v>
+        <v>223</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>2.772727272727273</v>
+        <v>4.590909090909091</v>
       </c>
       <c r="H49">
-        <v>0.08648838067322956</v>
+        <v>0.2901088360881014</v>
       </c>
       <c r="I49">
-        <v>39.2445</v>
+        <v>9.533250000000001</v>
       </c>
       <c r="J49">
-        <v>43.37549999999999</v>
+        <v>10.53675</v>
       </c>
       <c r="K49">
-        <v>0.6741536655230839</v>
+        <v>0.5550300658310013</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2731,13 +2731,13 @@
         <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D50">
-        <v>1455</v>
+        <v>321</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -2746,22 +2746,22 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>6.863636363636363</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="H50">
-        <v>0.04903484016480412</v>
+        <v>0.1998432951314664</v>
       </c>
       <c r="I50">
-        <v>130.95</v>
+        <v>13.72275</v>
       </c>
       <c r="J50">
-        <v>70.93125000000003</v>
+        <v>15.16725</v>
       </c>
       <c r="K50">
-        <v>0.6250273442582147</v>
+        <v>0.5503580257069358</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2787,7 +2787,7 @@
         <v>6.136363636363637</v>
       </c>
       <c r="H51">
-        <v>0.6433598442358975</v>
+        <v>0.5385169711538383</v>
       </c>
       <c r="I51">
         <v>7.199999999999999</v>
@@ -2796,10 +2796,10 @@
         <v>3.900000000000002</v>
       </c>
       <c r="K51">
-        <v>0.4508947700628138</v>
+        <v>0.3813404531485923</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2807,13 +2807,13 @@
         <v>81</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D52">
-        <v>1567</v>
+        <v>208</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -2822,22 +2822,22 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>4.818181818181818</v>
+        <v>4.318181818181818</v>
       </c>
       <c r="H52">
-        <v>0.01570351415061855</v>
+        <v>0.1817901869401397</v>
       </c>
       <c r="I52">
-        <v>66.98925</v>
+        <v>8.892000000000001</v>
       </c>
       <c r="J52">
-        <v>74.04075</v>
+        <v>9.827999999999998</v>
       </c>
       <c r="K52">
-        <v>0.2089413035310713</v>
+        <v>0.324402700504139</v>
       </c>
       <c r="L52" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2845,13 +2845,13 @@
         <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D53">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
@@ -2860,22 +2860,22 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>2.954545454545455</v>
+        <v>4.272727272727272</v>
       </c>
       <c r="H53">
-        <v>0.05458462090174051</v>
+        <v>0.1637370787488125</v>
       </c>
       <c r="I53">
-        <v>4.760000000000001</v>
+        <v>9.533250000000001</v>
       </c>
       <c r="J53">
-        <v>6.867999999999999</v>
+        <v>10.53675</v>
       </c>
       <c r="K53">
-        <v>0.06736855391657812</v>
+        <v>0.3132583027196413</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2883,13 +2883,13 @@
         <v>83</v>
       </c>
       <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
         <v>31</v>
       </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
       <c r="D54">
-        <v>2943</v>
+        <v>212</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
@@ -2898,22 +2898,22 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1.227272727272727</v>
+        <v>4.272727272727273</v>
       </c>
       <c r="H54">
-        <v>-0.6314334903687416</v>
+        <v>0.1637370787488129</v>
       </c>
       <c r="I54">
-        <v>51.5025</v>
+        <v>9.063000000000001</v>
       </c>
       <c r="J54">
-        <v>74.31075000000001</v>
+        <v>10.017</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>0.2978060994464757</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2921,13 +2921,13 @@
         <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D55">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
@@ -2936,22 +2936,22 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1.909090909090909</v>
+        <v>4.954545454545454</v>
       </c>
       <c r="H55">
-        <v>-0.3606368674987798</v>
+        <v>0.08642775890514701</v>
       </c>
       <c r="I55">
-        <v>1.225</v>
+        <v>5.635000000000001</v>
       </c>
       <c r="J55">
-        <v>1.7675</v>
+        <v>8.130500000000001</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>0.127590806535168</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2959,37 +2959,37 @@
         <v>85</v>
       </c>
       <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
         <v>31</v>
       </c>
-      <c r="C56" t="s">
-        <v>32</v>
-      </c>
       <c r="D56">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2.454545454545455</v>
+        <v>3.954545454545455</v>
       </c>
       <c r="H56">
-        <v>-0.1439995692028561</v>
+        <v>0.037365321409524</v>
       </c>
       <c r="I56">
-        <v>6.527500000000001</v>
+        <v>15.4755</v>
       </c>
       <c r="J56">
-        <v>9.41825</v>
+        <v>17.10449999999999</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>0.116045414072637</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2997,37 +2997,37 @@
         <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57">
-        <v>224</v>
+        <v>2943</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1.363636363636364</v>
+        <v>1.227272727272727</v>
       </c>
       <c r="H57">
-        <v>-0.4731579732579066</v>
+        <v>-1.39392711278366</v>
       </c>
       <c r="I57">
-        <v>9.576000000000001</v>
+        <v>51.5025</v>
       </c>
       <c r="J57">
-        <v>10.584</v>
+        <v>74.31075000000001</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3035,37 +3035,37 @@
         <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D58">
-        <v>556</v>
+        <v>453</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G58">
-        <v>3.363636363636363</v>
+        <v>2.409090909090909</v>
       </c>
       <c r="H58">
-        <v>-0.5619959479718446</v>
+        <v>-0.04137156467682958</v>
       </c>
       <c r="I58">
-        <v>23.769</v>
+        <v>7.927500000000001</v>
       </c>
       <c r="J58">
-        <v>26.271</v>
+        <v>11.43825</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3073,13 +3073,13 @@
         <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D59">
-        <v>413</v>
+        <v>881</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -3088,22 +3088,22 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>3.590909090909091</v>
+        <v>4.045454545454546</v>
       </c>
       <c r="H59">
-        <v>-0.4717304070152098</v>
+        <v>-0.2746344049213867</v>
       </c>
       <c r="I59">
-        <v>17.65575</v>
+        <v>15.4175</v>
       </c>
       <c r="J59">
-        <v>19.51425</v>
+        <v>22.24525</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3111,37 +3111,37 @@
         <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D60">
-        <v>425</v>
+        <v>676</v>
       </c>
       <c r="E60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>3.454545454545455</v>
+        <v>3.909090909090909</v>
       </c>
       <c r="H60">
-        <v>-0.5258897315891907</v>
+        <v>-0.3287937294953731</v>
       </c>
       <c r="I60">
-        <v>18.16875</v>
+        <v>11.83</v>
       </c>
       <c r="J60">
-        <v>20.08125</v>
+        <v>17.069</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3149,13 +3149,13 @@
         <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D61">
-        <v>680</v>
+        <v>272</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
@@ -3164,22 +3164,22 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>2.090909090909091</v>
+        <v>2.954545454545455</v>
       </c>
       <c r="H61">
-        <v>-1.067482977329</v>
+        <v>-0.7079090015132394</v>
       </c>
       <c r="I61">
-        <v>29.07</v>
+        <v>4.760000000000001</v>
       </c>
       <c r="J61">
-        <v>32.13</v>
+        <v>6.867999999999999</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3187,13 +3187,13 @@
         <v>91</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D62">
-        <v>2320</v>
+        <v>70</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
@@ -3202,22 +3202,22 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>3.045454545454545</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="H62">
-        <v>-0.6883677053111332</v>
+        <v>-1.12313048991376</v>
       </c>
       <c r="I62">
-        <v>99.18000000000001</v>
+        <v>1.225</v>
       </c>
       <c r="J62">
-        <v>109.62</v>
+        <v>1.7675</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3225,13 +3225,13 @@
         <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D63">
-        <v>212</v>
+        <v>373</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
@@ -3240,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>4.272727272727273</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="H63">
-        <v>-0.2009337841453049</v>
+        <v>-0.906493191617836</v>
       </c>
       <c r="I63">
-        <v>9.063000000000001</v>
+        <v>6.527500000000001</v>
       </c>
       <c r="J63">
-        <v>10.017</v>
+        <v>9.41825</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3263,37 +3263,37 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D64">
-        <v>1103</v>
+        <v>224</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G64">
-        <v>0.7727272727272727</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="H64">
-        <v>-1.591023114877482</v>
+        <v>-0.1084871103637888</v>
       </c>
       <c r="I64">
-        <v>47.15325000000001</v>
+        <v>9.576000000000001</v>
       </c>
       <c r="J64">
-        <v>52.11674999999999</v>
+        <v>10.584</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3301,13 +3301,13 @@
         <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D65">
-        <v>321</v>
+        <v>556</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
@@ -3316,22 +3316,22 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>4.363636363636363</v>
+        <v>3.363636363636363</v>
       </c>
       <c r="H65">
-        <v>-0.1648275677626514</v>
+        <v>-0.1973250850777268</v>
       </c>
       <c r="I65">
-        <v>13.72275</v>
+        <v>23.769</v>
       </c>
       <c r="J65">
-        <v>15.16725</v>
+        <v>26.271</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3339,37 +3339,37 @@
         <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D66">
-        <v>217</v>
+        <v>413</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>0.6818181818181819</v>
+        <v>3.590909090909091</v>
       </c>
       <c r="H66">
-        <v>-0.5881002311044596</v>
+        <v>-0.107059544121092</v>
       </c>
       <c r="I66">
-        <v>9.27675</v>
+        <v>17.65575</v>
       </c>
       <c r="J66">
-        <v>10.25325</v>
+        <v>19.51425</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3377,37 +3377,37 @@
         <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D67">
-        <v>189</v>
+        <v>425</v>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>3.727272727272728</v>
+        <v>3.454545454545455</v>
       </c>
       <c r="H67">
-        <v>-0.4175710824412287</v>
+        <v>-0.1612188686950728</v>
       </c>
       <c r="I67">
-        <v>8.079750000000001</v>
+        <v>18.16875</v>
       </c>
       <c r="J67">
-        <v>8.930249999999997</v>
+        <v>20.08125</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3415,13 +3415,13 @@
         <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D68">
-        <v>255</v>
+        <v>680</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -3430,22 +3430,22 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>2.590909090909091</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="H68">
-        <v>-0.8688987872244029</v>
+        <v>-0.702812114434882</v>
       </c>
       <c r="I68">
-        <v>10.90125</v>
+        <v>29.07</v>
       </c>
       <c r="J68">
-        <v>12.04875</v>
+        <v>32.13</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3453,13 +3453,13 @@
         <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D69">
-        <v>545</v>
+        <v>2320</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
@@ -3468,22 +3468,22 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>2.772727272727272</v>
+        <v>3.045454545454545</v>
       </c>
       <c r="H69">
-        <v>-0.7966863544590952</v>
+        <v>-0.3236968424170155</v>
       </c>
       <c r="I69">
-        <v>23.29875</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="J69">
-        <v>25.75125</v>
+        <v>109.62</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3491,13 +3491,13 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D70">
-        <v>718</v>
+        <v>1103</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -3506,22 +3506,22 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>4.590909090909091</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="H70">
-        <v>-0.07456202680601642</v>
+        <v>-1.226352251983364</v>
       </c>
       <c r="I70">
-        <v>30.6945</v>
+        <v>47.15325000000001</v>
       </c>
       <c r="J70">
-        <v>33.9255</v>
+        <v>52.11674999999999</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3529,37 +3529,37 @@
         <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D71">
-        <v>1190</v>
+        <v>217</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G71">
-        <v>0.8636363636363636</v>
+        <v>0.6818181818181819</v>
       </c>
       <c r="H71">
-        <v>-1.554916898494828</v>
+        <v>-0.2234293682103419</v>
       </c>
       <c r="I71">
-        <v>50.8725</v>
+        <v>9.27675</v>
       </c>
       <c r="J71">
-        <v>56.22749999999999</v>
+        <v>10.25325</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3567,37 +3567,37 @@
         <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D72">
-        <v>664</v>
+        <v>189</v>
       </c>
       <c r="E72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
-        <v>2.863636363636364</v>
+        <v>3.727272727272728</v>
       </c>
       <c r="H72">
-        <v>-0.7605801380764412</v>
+        <v>-0.05290021954711088</v>
       </c>
       <c r="I72">
-        <v>28.386</v>
+        <v>8.079750000000001</v>
       </c>
       <c r="J72">
-        <v>31.374</v>
+        <v>8.930249999999997</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3605,37 +3605,37 @@
         <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D73">
-        <v>362</v>
+        <v>255</v>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>3.954545454545455</v>
+        <v>2.590909090909091</v>
       </c>
       <c r="H73">
-        <v>-0.3273055414845938</v>
+        <v>-0.5042279243302852</v>
       </c>
       <c r="I73">
-        <v>15.4755</v>
+        <v>10.90125</v>
       </c>
       <c r="J73">
-        <v>17.10449999999999</v>
+        <v>12.04875</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3643,13 +3643,13 @@
         <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D74">
-        <v>314</v>
+        <v>545</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -3658,22 +3658,22 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>4.454545454545455</v>
+        <v>2.772727272727272</v>
       </c>
       <c r="H74">
-        <v>-0.1287213513799971</v>
+        <v>-0.4320154915649774</v>
       </c>
       <c r="I74">
-        <v>13.4235</v>
+        <v>23.29875</v>
       </c>
       <c r="J74">
-        <v>14.8365</v>
+        <v>25.75125</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3681,13 +3681,13 @@
         <v>104</v>
       </c>
       <c r="B75" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D75">
-        <v>1157</v>
+        <v>1190</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -3696,22 +3696,22 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>3.227272727272728</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="H75">
-        <v>-0.6161552725458252</v>
+        <v>-1.19024603560071</v>
       </c>
       <c r="I75">
-        <v>49.46175</v>
+        <v>50.8725</v>
       </c>
       <c r="J75">
-        <v>54.66824999999999</v>
+        <v>56.22749999999999</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3719,13 +3719,13 @@
         <v>105</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D76">
-        <v>1335</v>
+        <v>664</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
@@ -3734,22 +3734,22 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>1.727272727272727</v>
+        <v>2.863636363636364</v>
       </c>
       <c r="H76">
-        <v>-1.211907842859615</v>
+        <v>-0.3959092751823234</v>
       </c>
       <c r="I76">
-        <v>57.07125000000001</v>
+        <v>28.386</v>
       </c>
       <c r="J76">
-        <v>63.07874999999999</v>
+        <v>31.374</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3757,13 +3757,13 @@
         <v>106</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D77">
-        <v>216</v>
+        <v>1157</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
@@ -3772,22 +3772,22 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>1.363636363636364</v>
+        <v>3.227272727272728</v>
       </c>
       <c r="H77">
-        <v>-1.356332708390231</v>
+        <v>-0.2514844096517075</v>
       </c>
       <c r="I77">
-        <v>9.234</v>
+        <v>49.46175</v>
       </c>
       <c r="J77">
-        <v>10.206</v>
+        <v>54.66824999999999</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3795,13 +3795,13 @@
         <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D78">
-        <v>223</v>
+        <v>1335</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -3810,22 +3810,22 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>4.272727272727272</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="H78">
-        <v>-0.2009337841453053</v>
+        <v>-0.8472369799654975</v>
       </c>
       <c r="I78">
-        <v>9.533250000000001</v>
+        <v>57.07125000000001</v>
       </c>
       <c r="J78">
-        <v>10.53675</v>
+        <v>63.07874999999999</v>
       </c>
       <c r="K78">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3833,13 +3833,13 @@
         <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D79">
-        <v>976</v>
+        <v>216</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -3848,22 +3848,22 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>3.227272727272728</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="H79">
-        <v>-0.6161552725458252</v>
+        <v>-0.9916618454961135</v>
       </c>
       <c r="I79">
-        <v>41.724</v>
+        <v>9.234</v>
       </c>
       <c r="J79">
-        <v>46.116</v>
+        <v>10.206</v>
       </c>
       <c r="K79">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3871,13 +3871,13 @@
         <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D80">
-        <v>1690</v>
+        <v>976</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -3886,22 +3886,22 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>0.8636363636363636</v>
+        <v>3.227272727272728</v>
       </c>
       <c r="H80">
-        <v>-1.554916898494828</v>
+        <v>-0.2514844096517075</v>
       </c>
       <c r="I80">
-        <v>72.2475</v>
+        <v>41.724</v>
       </c>
       <c r="J80">
-        <v>79.85249999999999</v>
+        <v>46.116</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3909,13 +3909,13 @@
         <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D81">
-        <v>2267</v>
+        <v>1690</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -3924,22 +3924,22 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>3.727272727272728</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="H81">
-        <v>-0.4175710824412287</v>
+        <v>-1.19024603560071</v>
       </c>
       <c r="I81">
-        <v>96.91425000000001</v>
+        <v>72.2475</v>
       </c>
       <c r="J81">
-        <v>107.11575</v>
+        <v>79.85249999999999</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3947,13 +3947,13 @@
         <v>111</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D82">
-        <v>223</v>
+        <v>2267</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -3962,22 +3962,22 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>4.590909090909091</v>
+        <v>3.727272727272728</v>
       </c>
       <c r="H82">
-        <v>-0.07456202680601642</v>
+        <v>-0.05290021954711088</v>
       </c>
       <c r="I82">
-        <v>9.533250000000001</v>
+        <v>96.91425000000001</v>
       </c>
       <c r="J82">
-        <v>10.53675</v>
+        <v>107.11575</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3985,10 +3985,10 @@
         <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D83">
         <v>203</v>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <v>-1.89792595413004</v>
+        <v>-1.533255091235922</v>
       </c>
       <c r="I83">
         <v>8.67825</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4023,7 +4023,7 @@
         <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C84" t="s">
         <v>29</v>
@@ -4041,7 +4041,7 @@
         <v>1.5</v>
       </c>
       <c r="H84">
-        <v>-1.30217338381625</v>
+        <v>-0.9375025209221326</v>
       </c>
       <c r="I84">
         <v>89.98875000000001</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4061,7 +4061,7 @@
         <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
         <v>29</v>
@@ -4079,7 +4079,7 @@
         <v>0.8636363636363636</v>
       </c>
       <c r="H85">
-        <v>-1.554916898494828</v>
+        <v>-1.19024603560071</v>
       </c>
       <c r="I85">
         <v>98.06850000000001</v>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4099,7 +4099,7 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -4117,7 +4117,7 @@
         <v>2.318181818181818</v>
       </c>
       <c r="H86">
-        <v>-0.9772174363723647</v>
+        <v>-0.6125465734782469</v>
       </c>
       <c r="I86">
         <v>13.89375</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4137,10 +4137,10 @@
         <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D87">
         <v>572</v>
@@ -4155,7 +4155,7 @@
         <v>1.636363636363636</v>
       </c>
       <c r="H87">
-        <v>-1.248014059242269</v>
+        <v>-0.8833431963481517</v>
       </c>
       <c r="I87">
         <v>24.453</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4175,10 +4175,10 @@
         <v>117</v>
       </c>
       <c r="B88" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D88">
         <v>1064</v>
@@ -4193,7 +4193,7 @@
         <v>3.545454545454546</v>
       </c>
       <c r="H88">
-        <v>-0.4897835152065365</v>
+        <v>-0.1251126523124186</v>
       </c>
       <c r="I88">
         <v>45.486</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4213,7 +4213,7 @@
         <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -4231,7 +4231,7 @@
         <v>2.954545454545455</v>
       </c>
       <c r="H89">
-        <v>-0.7244739216937872</v>
+        <v>-0.3598030587996695</v>
       </c>
       <c r="I89">
         <v>35.35425</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4251,37 +4251,37 @@
         <v>119</v>
       </c>
       <c r="B90" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D90">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
         <v>0</v>
       </c>
       <c r="G90">
-        <v>4.318181818181818</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="H90">
-        <v>-0.1828806759539782</v>
+        <v>-0.1251126523124186</v>
       </c>
       <c r="I90">
-        <v>8.892000000000001</v>
+        <v>6.7545</v>
       </c>
       <c r="J90">
-        <v>9.827999999999998</v>
+        <v>7.465499999999999</v>
       </c>
       <c r="K90">
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4289,13 +4289,13 @@
         <v>120</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D91">
-        <v>158</v>
+        <v>1077</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -4304,22 +4304,22 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>3.545454545454546</v>
+        <v>2.363636363636363</v>
       </c>
       <c r="H91">
-        <v>-0.4897835152065365</v>
+        <v>-1.843065743858625</v>
       </c>
       <c r="I91">
-        <v>6.7545</v>
+        <v>96.92999999999999</v>
       </c>
       <c r="J91">
-        <v>7.465499999999999</v>
+        <v>52.50375000000001</v>
       </c>
       <c r="K91">
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4330,10 +4330,10 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D92">
-        <v>1077</v>
+        <v>1027</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
@@ -4342,22 +4342,22 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>2.363636363636363</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="H92">
-        <v>-1.738222870776566</v>
+        <v>-2.312446556833126</v>
       </c>
       <c r="I92">
-        <v>96.92999999999999</v>
+        <v>92.42999999999999</v>
       </c>
       <c r="J92">
-        <v>52.50375000000001</v>
+        <v>50.06625000000001</v>
       </c>
       <c r="K92">
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4368,10 +4368,10 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D93">
-        <v>1027</v>
+        <v>597</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -4380,22 +4380,22 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1.181818181818182</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="H93">
-        <v>-2.207603683751067</v>
+        <v>-0.9765165506749302</v>
       </c>
       <c r="I93">
-        <v>92.42999999999999</v>
+        <v>53.73</v>
       </c>
       <c r="J93">
-        <v>50.06625000000001</v>
+        <v>29.10375000000001</v>
       </c>
       <c r="K93">
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4406,10 +4406,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D94">
-        <v>597</v>
+        <v>3746</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
@@ -4418,22 +4418,22 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>4.545454545454546</v>
+        <v>3.909090909090909</v>
       </c>
       <c r="H94">
-        <v>-0.8716736775928708</v>
+        <v>-1.229260065353508</v>
       </c>
       <c r="I94">
-        <v>53.73</v>
+        <v>337.14</v>
       </c>
       <c r="J94">
-        <v>29.10375000000001</v>
+        <v>182.6175000000001</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4444,10 +4444,10 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D95">
-        <v>3746</v>
+        <v>769</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -4456,22 +4456,22 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>3.909090909090909</v>
+        <v>4.409090909090909</v>
       </c>
       <c r="H95">
-        <v>-1.124417192271449</v>
+        <v>-1.030675875248911</v>
       </c>
       <c r="I95">
-        <v>337.14</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="J95">
-        <v>182.6175000000001</v>
+        <v>37.48875000000001</v>
       </c>
       <c r="K95">
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4482,10 +4482,10 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D96">
-        <v>769</v>
+        <v>384</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
@@ -4494,22 +4494,22 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>4.409090909090909</v>
+        <v>4.318181818181818</v>
       </c>
       <c r="H96">
-        <v>-0.9258330021668519</v>
+        <v>-1.066782091631565</v>
       </c>
       <c r="I96">
-        <v>69.20999999999999</v>
+        <v>34.56</v>
       </c>
       <c r="J96">
-        <v>37.48875000000001</v>
+        <v>18.72</v>
       </c>
       <c r="K96">
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4520,34 +4520,34 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D97">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97">
-        <v>4.318181818181818</v>
+        <v>2.272727272727272</v>
       </c>
       <c r="H97">
-        <v>-0.9619392185495059</v>
+        <v>-1.879171960241279</v>
       </c>
       <c r="I97">
-        <v>34.56</v>
+        <v>28.62</v>
       </c>
       <c r="J97">
-        <v>18.72</v>
+        <v>15.5025</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4558,34 +4558,34 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D98">
-        <v>318</v>
+        <v>638</v>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G98">
-        <v>2.272727272727272</v>
+        <v>2.954545454545455</v>
       </c>
       <c r="H98">
-        <v>-1.774329087159219</v>
+        <v>-0.8291035122546172</v>
       </c>
       <c r="I98">
-        <v>28.62</v>
+        <v>57.41999999999999</v>
       </c>
       <c r="J98">
-        <v>15.5025</v>
+        <v>31.10250000000001</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4596,34 +4596,34 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D99">
-        <v>638</v>
+        <v>1334</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
       </c>
       <c r="F99">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>2.954545454545455</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="H99">
-        <v>-0.7242606391725579</v>
+        <v>-1.951384393006587</v>
       </c>
       <c r="I99">
-        <v>57.41999999999999</v>
+        <v>120.06</v>
       </c>
       <c r="J99">
-        <v>31.10250000000001</v>
+        <v>65.03250000000003</v>
       </c>
       <c r="K99">
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4634,10 +4634,10 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D100">
-        <v>1334</v>
+        <v>532</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -4646,22 +4646,22 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>2.090909090909091</v>
+        <v>6.181818181818182</v>
       </c>
       <c r="H100">
-        <v>-1.846541519924527</v>
+        <v>-0.3266046557871596</v>
       </c>
       <c r="I100">
-        <v>120.06</v>
+        <v>47.88</v>
       </c>
       <c r="J100">
-        <v>65.03250000000003</v>
+        <v>25.93500000000002</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>532</v>
+        <v>189</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -4684,22 +4684,22 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>6.181818181818182</v>
+        <v>3.272727272727272</v>
       </c>
       <c r="H101">
-        <v>-0.2217617827051004</v>
+        <v>-1.482003580032086</v>
       </c>
       <c r="I101">
-        <v>47.88</v>
+        <v>17.01</v>
       </c>
       <c r="J101">
-        <v>25.93500000000002</v>
+        <v>9.213750000000005</v>
       </c>
       <c r="K101">
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4710,10 +4710,10 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D102">
-        <v>189</v>
+        <v>395</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -4722,22 +4722,22 @@
         <v>0</v>
       </c>
       <c r="G102">
-        <v>3.272727272727272</v>
+        <v>2.681818181818182</v>
       </c>
       <c r="H102">
-        <v>-1.377160706950026</v>
+        <v>-1.716693986519336</v>
       </c>
       <c r="I102">
-        <v>17.01</v>
+        <v>35.55</v>
       </c>
       <c r="J102">
-        <v>9.213750000000005</v>
+        <v>19.25625000000001</v>
       </c>
       <c r="K102">
         <v>0</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4748,34 +4748,34 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D103">
-        <v>395</v>
+        <v>514</v>
       </c>
       <c r="E103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103">
-        <v>2.681818181818182</v>
+        <v>5.045454545454546</v>
       </c>
       <c r="H103">
-        <v>-1.611851113437277</v>
+        <v>-0.7779323605703335</v>
       </c>
       <c r="I103">
-        <v>35.55</v>
+        <v>46.26</v>
       </c>
       <c r="J103">
-        <v>19.25625000000001</v>
+        <v>25.05750000000001</v>
       </c>
       <c r="K103">
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4786,34 +4786,34 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D104">
-        <v>514</v>
+        <v>1461</v>
       </c>
       <c r="E104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104">
-        <v>5.045454545454546</v>
+        <v>3.545454545454545</v>
       </c>
       <c r="H104">
-        <v>-0.6730894874882742</v>
+        <v>-1.373684930884124</v>
       </c>
       <c r="I104">
-        <v>46.26</v>
+        <v>131.49</v>
       </c>
       <c r="J104">
-        <v>25.05750000000001</v>
+        <v>71.22375</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4824,10 +4824,10 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D105">
-        <v>1461</v>
+        <v>506</v>
       </c>
       <c r="E105" t="b">
         <v>1</v>
@@ -4836,22 +4836,22 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>3.545454545454545</v>
+        <v>4.954545454545455</v>
       </c>
       <c r="H105">
-        <v>-1.268842057802064</v>
+        <v>-0.8140385769529874</v>
       </c>
       <c r="I105">
-        <v>131.49</v>
+        <v>45.54</v>
       </c>
       <c r="J105">
-        <v>71.22375</v>
+        <v>24.66750000000001</v>
       </c>
       <c r="K105">
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4865,7 +4865,7 @@
         <v>14</v>
       </c>
       <c r="D106">
-        <v>506</v>
+        <v>1084</v>
       </c>
       <c r="E106" t="b">
         <v>1</v>
@@ -4874,22 +4874,22 @@
         <v>0</v>
       </c>
       <c r="G106">
-        <v>4.954545454545455</v>
+        <v>5.590909090909091</v>
       </c>
       <c r="H106">
-        <v>-0.7091957038709282</v>
+        <v>-0.5612950622744102</v>
       </c>
       <c r="I106">
-        <v>45.54</v>
+        <v>97.56</v>
       </c>
       <c r="J106">
-        <v>24.66750000000001</v>
+        <v>52.845</v>
       </c>
       <c r="K106">
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4900,10 +4900,10 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D107">
-        <v>1084</v>
+        <v>444</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -4912,22 +4912,22 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>5.590909090909091</v>
+        <v>2.409090909090909</v>
       </c>
       <c r="H107">
-        <v>-0.4564521891923509</v>
+        <v>-1.825012635667298</v>
       </c>
       <c r="I107">
-        <v>97.56</v>
+        <v>39.96</v>
       </c>
       <c r="J107">
-        <v>52.845</v>
+        <v>21.645</v>
       </c>
       <c r="K107">
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4938,10 +4938,10 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D108">
-        <v>444</v>
+        <v>733</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
@@ -4950,22 +4950,22 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>2.409090909090909</v>
+        <v>3.590909090909091</v>
       </c>
       <c r="H108">
-        <v>-1.720169762585239</v>
+        <v>-1.355631822692797</v>
       </c>
       <c r="I108">
-        <v>39.96</v>
+        <v>65.97</v>
       </c>
       <c r="J108">
-        <v>21.645</v>
+        <v>35.73375000000001</v>
       </c>
       <c r="K108">
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4976,10 +4976,10 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D109">
-        <v>733</v>
+        <v>336</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -4988,22 +4988,22 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>3.590909090909091</v>
+        <v>4.409090909090909</v>
       </c>
       <c r="H109">
-        <v>-1.250788949610737</v>
+        <v>-1.030675875248911</v>
       </c>
       <c r="I109">
-        <v>65.97</v>
+        <v>30.24</v>
       </c>
       <c r="J109">
-        <v>35.73375000000001</v>
+        <v>16.38000000000001</v>
       </c>
       <c r="K109">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5014,10 +5014,10 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D110">
-        <v>336</v>
+        <v>674</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -5026,22 +5026,22 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>4.409090909090909</v>
+        <v>3.954545454545455</v>
       </c>
       <c r="H110">
-        <v>-0.9258330021668519</v>
+        <v>-1.211206957162181</v>
       </c>
       <c r="I110">
-        <v>30.24</v>
+        <v>60.66</v>
       </c>
       <c r="J110">
-        <v>16.38000000000001</v>
+        <v>32.85750000000002</v>
       </c>
       <c r="K110">
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5055,7 +5055,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>674</v>
+        <v>248</v>
       </c>
       <c r="E111" t="b">
         <v>1</v>
@@ -5064,22 +5064,22 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>3.954545454545455</v>
+        <v>4</v>
       </c>
       <c r="H111">
-        <v>-1.106364084080121</v>
+        <v>-1.193153848970854</v>
       </c>
       <c r="I111">
-        <v>60.66</v>
+        <v>22.32</v>
       </c>
       <c r="J111">
-        <v>32.85750000000002</v>
+        <v>12.09</v>
       </c>
       <c r="K111">
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5090,10 +5090,10 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D112">
-        <v>248</v>
+        <v>350</v>
       </c>
       <c r="E112" t="b">
         <v>1</v>
@@ -5102,22 +5102,22 @@
         <v>0</v>
       </c>
       <c r="G112">
-        <v>4</v>
+        <v>6.136363636363637</v>
       </c>
       <c r="H112">
-        <v>-1.088310975888795</v>
+        <v>-0.3446577639784864</v>
       </c>
       <c r="I112">
-        <v>22.32</v>
+        <v>31.5</v>
       </c>
       <c r="J112">
-        <v>12.09</v>
+        <v>17.06250000000001</v>
       </c>
       <c r="K112">
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5128,10 +5128,10 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D113">
-        <v>350</v>
+        <v>561</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
@@ -5140,22 +5140,22 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>6.136363636363637</v>
+        <v>5.863636363636364</v>
       </c>
       <c r="H113">
-        <v>-0.2398148908964271</v>
+        <v>-0.4529764131264482</v>
       </c>
       <c r="I113">
-        <v>31.5</v>
+        <v>50.48999999999999</v>
       </c>
       <c r="J113">
-        <v>17.06250000000001</v>
+        <v>27.34875000000001</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5166,10 +5166,10 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D114">
-        <v>561</v>
+        <v>615</v>
       </c>
       <c r="E114" t="b">
         <v>1</v>
@@ -5178,22 +5178,22 @@
         <v>0</v>
       </c>
       <c r="G114">
-        <v>5.863636363636364</v>
+        <v>4.863636363636363</v>
       </c>
       <c r="H114">
-        <v>-0.3481335400443888</v>
+        <v>-0.8501447933356416</v>
       </c>
       <c r="I114">
-        <v>50.48999999999999</v>
+        <v>55.35</v>
       </c>
       <c r="J114">
-        <v>27.34875000000001</v>
+        <v>29.98125000000001</v>
       </c>
       <c r="K114">
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5204,34 +5204,34 @@
         <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D115">
-        <v>615</v>
+        <v>63</v>
       </c>
       <c r="E115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>0</v>
       </c>
       <c r="G115">
-        <v>4.863636363636363</v>
+        <v>5.863636363636363</v>
       </c>
       <c r="H115">
-        <v>-0.7453019202535824</v>
+        <v>-0.4529764131264485</v>
       </c>
       <c r="I115">
-        <v>55.35</v>
+        <v>5.67</v>
       </c>
       <c r="J115">
-        <v>29.98125000000001</v>
+        <v>3.071250000000001</v>
       </c>
       <c r="K115">
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5245,31 +5245,31 @@
         <v>14</v>
       </c>
       <c r="D116">
-        <v>63</v>
+        <v>2141</v>
       </c>
       <c r="E116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116">
         <v>0</v>
       </c>
       <c r="G116">
-        <v>5.863636363636363</v>
+        <v>6.363636363636364</v>
       </c>
       <c r="H116">
-        <v>-0.3481335400443892</v>
+        <v>-0.2543922230218514</v>
       </c>
       <c r="I116">
-        <v>5.67</v>
+        <v>192.69</v>
       </c>
       <c r="J116">
-        <v>3.071250000000001</v>
+        <v>104.37375</v>
       </c>
       <c r="K116">
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5280,10 +5280,10 @@
         <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D117">
-        <v>2141</v>
+        <v>457</v>
       </c>
       <c r="E117" t="b">
         <v>1</v>
@@ -5292,22 +5292,22 @@
         <v>0</v>
       </c>
       <c r="G117">
-        <v>6.363636363636364</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="H117">
-        <v>-0.1495493499397922</v>
+        <v>-1.662534661945355</v>
       </c>
       <c r="I117">
-        <v>192.69</v>
+        <v>41.13</v>
       </c>
       <c r="J117">
-        <v>104.37375</v>
+        <v>22.27875000000001</v>
       </c>
       <c r="K117">
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5318,10 +5318,10 @@
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D118">
-        <v>457</v>
+        <v>350</v>
       </c>
       <c r="E118" t="b">
         <v>1</v>
@@ -5330,22 +5330,22 @@
         <v>0</v>
       </c>
       <c r="G118">
-        <v>2.818181818181818</v>
+        <v>4.818181818181818</v>
       </c>
       <c r="H118">
-        <v>-1.557691788863296</v>
+        <v>-0.8681979015269684</v>
       </c>
       <c r="I118">
-        <v>41.13</v>
+        <v>31.5</v>
       </c>
       <c r="J118">
-        <v>22.27875000000001</v>
+        <v>17.06250000000001</v>
       </c>
       <c r="K118">
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5356,10 +5356,10 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D119">
-        <v>350</v>
+        <v>611</v>
       </c>
       <c r="E119" t="b">
         <v>1</v>
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="G119">
-        <v>4.818181818181818</v>
+        <v>1.954545454545455</v>
       </c>
       <c r="H119">
-        <v>-0.7633550284449091</v>
+        <v>-2.005543717580568</v>
       </c>
       <c r="I119">
-        <v>31.5</v>
+        <v>54.98999999999999</v>
       </c>
       <c r="J119">
-        <v>17.06250000000001</v>
+        <v>29.78625000000001</v>
       </c>
       <c r="K119">
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5394,10 +5394,10 @@
         <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D120">
-        <v>611</v>
+        <v>851</v>
       </c>
       <c r="E120" t="b">
         <v>1</v>
@@ -5406,22 +5406,22 @@
         <v>0</v>
       </c>
       <c r="G120">
-        <v>1.954545454545455</v>
+        <v>3.727272727272728</v>
       </c>
       <c r="H120">
-        <v>-1.900700844498508</v>
+        <v>-1.301472498118816</v>
       </c>
       <c r="I120">
-        <v>54.98999999999999</v>
+        <v>76.59</v>
       </c>
       <c r="J120">
-        <v>29.78625000000001</v>
+        <v>41.48625000000001</v>
       </c>
       <c r="K120">
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5432,34 +5432,34 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D121">
-        <v>851</v>
+        <v>218</v>
       </c>
       <c r="E121" t="b">
         <v>1</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G121">
-        <v>3.727272727272728</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="H121">
-        <v>-1.196629625036757</v>
+        <v>-1.327576781251431</v>
       </c>
       <c r="I121">
-        <v>76.59</v>
+        <v>19.62</v>
       </c>
       <c r="J121">
-        <v>41.48625000000001</v>
+        <v>10.6275</v>
       </c>
       <c r="K121">
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5470,34 +5470,34 @@
         <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D122">
-        <v>218</v>
+        <v>661</v>
       </c>
       <c r="E122" t="b">
         <v>1</v>
       </c>
       <c r="F122">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>1.045454545454545</v>
+        <v>3.454545454545455</v>
       </c>
       <c r="H122">
-        <v>-1.222733908169372</v>
+        <v>-1.409791147266778</v>
       </c>
       <c r="I122">
-        <v>19.62</v>
+        <v>59.48999999999999</v>
       </c>
       <c r="J122">
-        <v>10.6275</v>
+        <v>32.22375000000001</v>
       </c>
       <c r="K122">
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5508,10 +5508,10 @@
         <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D123">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="E123" t="b">
         <v>1</v>
@@ -5520,22 +5520,22 @@
         <v>0</v>
       </c>
       <c r="G123">
-        <v>3.454545454545455</v>
+        <v>5.772727272727272</v>
       </c>
       <c r="H123">
-        <v>-1.304948274184718</v>
+        <v>-0.4890826295091024</v>
       </c>
       <c r="I123">
-        <v>59.48999999999999</v>
+        <v>62.64</v>
       </c>
       <c r="J123">
-        <v>32.22375000000001</v>
+        <v>33.93000000000001</v>
       </c>
       <c r="K123">
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5546,10 +5546,10 @@
         <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D124">
-        <v>696</v>
+        <v>1455</v>
       </c>
       <c r="E124" t="b">
         <v>1</v>
@@ -5558,22 +5558,22 @@
         <v>0</v>
       </c>
       <c r="G124">
-        <v>5.772727272727272</v>
+        <v>6.863636363636363</v>
       </c>
       <c r="H124">
-        <v>-0.3842397564270431</v>
+        <v>-0.0558080329172551</v>
       </c>
       <c r="I124">
-        <v>62.64</v>
+        <v>130.95</v>
       </c>
       <c r="J124">
-        <v>33.93000000000001</v>
+        <v>70.93125000000003</v>
       </c>
       <c r="K124">
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5599,7 +5599,7 @@
         <v>3.454545454545455</v>
       </c>
       <c r="H125">
-        <v>-0.2139677190212584</v>
+        <v>-0.3188105921033176</v>
       </c>
       <c r="I125">
         <v>26.73</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5637,7 +5637,7 @@
         <v>4.863636363636363</v>
       </c>
       <c r="H126">
-        <v>-0.7453019202535824</v>
+        <v>-0.8501447933356416</v>
       </c>
       <c r="I126">
         <v>638.91</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5660,7 +5660,7 @@
         <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D127">
         <v>458</v>
@@ -5675,7 +5675,7 @@
         <v>2.590909090909091</v>
       </c>
       <c r="H127">
-        <v>-1.647957329819931</v>
+        <v>-1.75280020290199</v>
       </c>
       <c r="I127">
         <v>41.22</v>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5713,7 +5713,7 @@
         <v>5.5</v>
       </c>
       <c r="H128">
-        <v>-0.4925584055750048</v>
+        <v>-0.5974012786570642</v>
       </c>
       <c r="I128">
         <v>125.82</v>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5751,7 +5751,7 @@
         <v>3.045454545454545</v>
       </c>
       <c r="H129">
-        <v>-1.467426247906661</v>
+        <v>-1.57226912098872</v>
       </c>
       <c r="I129">
         <v>123.57</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="L129" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5774,7 +5774,7 @@
         <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D130">
         <v>416</v>
@@ -5789,7 +5789,7 @@
         <v>4.5</v>
       </c>
       <c r="H130">
-        <v>-0.05850350565965724</v>
+        <v>-0.1633463787417165</v>
       </c>
       <c r="I130">
         <v>37.44</v>
@@ -5801,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="L130" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5827,7 +5827,7 @@
         <v>2.863636363636364</v>
       </c>
       <c r="H131">
-        <v>-0.708415400547428</v>
+        <v>-0.8132582736294873</v>
       </c>
       <c r="I131">
         <v>795.51</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5850,7 +5850,7 @@
         <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D132">
         <v>255</v>
@@ -5865,7 +5865,7 @@
         <v>3.590909090909091</v>
       </c>
       <c r="H132">
-        <v>-0.4715171244939803</v>
+        <v>-0.5763599975760396</v>
       </c>
       <c r="I132">
         <v>22.95</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -5903,7 +5903,7 @@
         <v>4.090909090909091</v>
       </c>
       <c r="H133">
-        <v>-0.2729329343893838</v>
+        <v>-0.3777758074714431</v>
       </c>
       <c r="I133">
         <v>101.97</v>
@@ -5915,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5926,7 +5926,7 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D134">
         <v>1092</v>
@@ -5941,7 +5941,7 @@
         <v>3.545454545454545</v>
       </c>
       <c r="H134">
-        <v>-1.268842057802064</v>
+        <v>-1.373684930884124</v>
       </c>
       <c r="I134">
         <v>98.28</v>
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -5964,7 +5964,7 @@
         <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D135">
         <v>603</v>
@@ -5979,7 +5979,7 @@
         <v>3.136363636363637</v>
       </c>
       <c r="H135">
-        <v>-1.431320031524007</v>
+        <v>-1.536162904606067</v>
       </c>
       <c r="I135">
         <v>54.27</v>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -6002,7 +6002,7 @@
         <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D136">
         <v>651</v>
@@ -6017,7 +6017,7 @@
         <v>3.409090909090909</v>
       </c>
       <c r="H136">
-        <v>-0.2839722822203693</v>
+        <v>-0.3888151553024286</v>
       </c>
       <c r="I136">
         <v>58.59</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6040,7 +6040,7 @@
         <v>13</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D137">
         <v>1791</v>
@@ -6055,7 +6055,7 @@
         <v>3.863636363636364</v>
       </c>
       <c r="H137">
-        <v>-1.142470300462776</v>
+        <v>-1.247313173544835</v>
       </c>
       <c r="I137">
         <v>161.19</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6078,7 +6078,7 @@
         <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D138">
         <v>687</v>
@@ -6093,7 +6093,7 @@
         <v>3.363636363636364</v>
       </c>
       <c r="H138">
-        <v>-1.341054490567372</v>
+        <v>-1.445897363649431</v>
       </c>
       <c r="I138">
         <v>61.83</v>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -6158,13 +6158,13 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>676</v>
@@ -6179,7 +6179,7 @@
         <v>3.909090909090909</v>
       </c>
       <c r="H2">
-        <v>0.4336998929196069</v>
+        <v>-0.3287937294953731</v>
       </c>
       <c r="I2">
         <v>11.83</v>
@@ -6188,18 +6188,18 @@
         <v>17.069</v>
       </c>
       <c r="K2">
-        <v>1.330313608153474</v>
+        <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -6217,7 +6217,7 @@
         <v>6.363636363636363</v>
       </c>
       <c r="H3">
-        <v>2.239791015375804</v>
+        <v>1.477297392960824</v>
       </c>
       <c r="I3">
         <v>3.885</v>
@@ -6226,18 +6226,18 @@
         <v>5.605500000000001</v>
       </c>
       <c r="K3">
-        <v>2.256204678305126</v>
+        <v>1.503596011879484</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -6255,7 +6255,7 @@
         <v>4.818181818181818</v>
       </c>
       <c r="H4">
-        <v>0.01570351415061855</v>
+        <v>0.3803743770447364</v>
       </c>
       <c r="I4">
         <v>66.98925</v>
@@ -6264,21 +6264,21 @@
         <v>74.04075</v>
       </c>
       <c r="K4">
-        <v>0.2089413035310713</v>
+        <v>5.113649299217015</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>189</v>
@@ -6293,7 +6293,7 @@
         <v>3.727272727272728</v>
       </c>
       <c r="H5">
-        <v>-0.4175710824412287</v>
+        <v>-0.05290021954711088</v>
       </c>
       <c r="I5">
         <v>8.079750000000001</v>
@@ -6305,18 +6305,18 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>1491</v>
@@ -6331,7 +6331,7 @@
         <v>3.818181818181818</v>
       </c>
       <c r="H6">
-        <v>0.5536613240815337</v>
+        <v>0.9183321869756514</v>
       </c>
       <c r="I6">
         <v>63.74025</v>
@@ -6340,21 +6340,21 @@
         <v>70.44974999999999</v>
       </c>
       <c r="K6">
-        <v>7.009390951615226</v>
+        <v>11.74703166542399</v>
       </c>
       <c r="L6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>362</v>
@@ -6369,7 +6369,7 @@
         <v>3.954545454545455</v>
       </c>
       <c r="H7">
-        <v>-0.3273055414845938</v>
+        <v>0.037365321409524</v>
       </c>
       <c r="I7">
         <v>15.4755</v>
@@ -6378,10 +6378,10 @@
         <v>17.10449999999999</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.116045414072637</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -6389,7 +6389,7 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -6407,7 +6407,7 @@
         <v>2.318181818181818</v>
       </c>
       <c r="H8">
-        <v>-0.9772174363723647</v>
+        <v>-0.6125465734782469</v>
       </c>
       <c r="I8">
         <v>13.89375</v>
@@ -6419,18 +6419,18 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>208</v>
@@ -6445,7 +6445,7 @@
         <v>4.318181818181818</v>
       </c>
       <c r="H9">
-        <v>-0.1828806759539782</v>
+        <v>0.1817901869401397</v>
       </c>
       <c r="I9">
         <v>8.892000000000001</v>
@@ -6454,10 +6454,10 @@
         <v>9.827999999999998</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.324402700504139</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
